--- a/B/chrXI:0-95258_61_finemapping.xlsx
+++ b/B/chrXI:0-95258_61_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3548" uniqueCount="3548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3540" uniqueCount="3540">
   <si>
     <t xml:space="preserve">seqnames</t>
   </si>
@@ -9764,19 +9764,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -10266,21 +10257,6 @@
   </si>
   <si>
     <t xml:space="preserve">VMA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -11202,48 +11178,42 @@
         <v>3246</v>
       </c>
       <c r="Z1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3247</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3248</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3249</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3250</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3251</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3252</v>
       </c>
-      <c r="AF1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3253</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3254</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3255</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3256</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>3258</v>
+        <v>3255</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
@@ -11297,59 +11267,57 @@
         <v>52628</v>
       </c>
       <c r="U2" t="s">
-        <v>3259</v>
+        <v>3256</v>
       </c>
       <c r="V2" t="n">
         <v>162825</v>
       </c>
       <c r="W2" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.206449730095972</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0468815329204624</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3259</v>
       </c>
       <c r="AD2" t="s">
         <v>30</v>
       </c>
       <c r="AE2" t="s">
-        <v>3262</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3262</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>3259</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="b">
+      <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>3263</v>
+      <c r="AH2" t="s">
+        <v>3260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>3264</v>
+        <v>3261</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
@@ -11403,59 +11371,57 @@
         <v>52628</v>
       </c>
       <c r="U3" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="V3" t="n">
         <v>481244</v>
       </c>
       <c r="W3" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.102006665738138</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0232462717258762</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3263</v>
       </c>
       <c r="AD3" t="s">
         <v>30</v>
       </c>
       <c r="AE3" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3263</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AI3" t="b">
+      <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>3267</v>
+      <c r="AH3" t="s">
+        <v>3264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>3268</v>
+        <v>3265</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -11509,62 +11475,60 @@
         <v>77001</v>
       </c>
       <c r="U4" t="s">
-        <v>3269</v>
+        <v>3266</v>
       </c>
       <c r="V4" t="n">
         <v>352414</v>
       </c>
       <c r="W4" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.106833745157017</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0258387849180909</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3267</v>
       </c>
       <c r="AD4" t="s">
         <v>30</v>
       </c>
       <c r="AE4" t="s">
-        <v>3270</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3270</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>3267</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
-      <c r="AI4" t="b">
+      <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>3271</v>
+      <c r="AH4" t="s">
+        <v>3268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>3272</v>
+        <v>3269</v>
       </c>
       <c r="D5" t="s">
-        <v>3273</v>
+        <v>3270</v>
       </c>
       <c r="E5" t="n">
         <v>77001</v>
@@ -11615,59 +11579,57 @@
         <v>80882</v>
       </c>
       <c r="U5" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V5" t="n">
         <v>663099</v>
       </c>
       <c r="W5" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.124122031024087</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.03068422552627</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3272</v>
       </c>
       <c r="AD5" t="s">
         <v>30</v>
       </c>
       <c r="AE5" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="b">
+      <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>3276</v>
+      <c r="AH5" t="s">
+        <v>3273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>3277</v>
+        <v>3274</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -11721,59 +11683,57 @@
         <v>77001</v>
       </c>
       <c r="U6" t="s">
-        <v>3269</v>
+        <v>3266</v>
       </c>
       <c r="V6" t="n">
         <v>196306</v>
       </c>
       <c r="W6" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.123257826752512</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0324796044432899</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3267</v>
       </c>
       <c r="AD6" t="s">
         <v>30</v>
       </c>
       <c r="AE6" t="s">
-        <v>3270</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3270</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>3278</v>
+        <v>3267</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3275</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>3279</v>
+        <v>3276</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -11827,59 +11787,57 @@
         <v>77001</v>
       </c>
       <c r="U7" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="V7" t="n">
         <v>725814</v>
       </c>
       <c r="W7" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.154831664327465</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0403332842425919</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3278</v>
       </c>
       <c r="AD7" t="s">
         <v>30</v>
       </c>
       <c r="AE7" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3282</v>
+        <v>3278</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>3283</v>
+        <v>3280</v>
       </c>
       <c r="D8" t="s">
         <v>193</v>
@@ -11933,27 +11891,31 @@
         <v>39867</v>
       </c>
       <c r="U8" t="s">
-        <v>3284</v>
+        <v>3281</v>
       </c>
       <c r="V8" t="n">
         <v>572195</v>
       </c>
       <c r="W8" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.0603423568229292</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0161442039753707</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>45</v>
       </c>
       <c r="AD8" t="s">
         <v>30</v>
@@ -11961,31 +11923,25 @@
       <c r="AE8" t="s">
         <v>45</v>
       </c>
-      <c r="AF8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" t="b">
+      <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>3287</v>
+      <c r="AH8" t="s">
+        <v>3284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>3288</v>
+        <v>3285</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -12039,59 +11995,57 @@
         <v>77001</v>
       </c>
       <c r="U9" t="s">
-        <v>3289</v>
+        <v>3286</v>
       </c>
       <c r="V9" t="n">
         <v>784857</v>
       </c>
       <c r="W9" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.147424981105086</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0430532220982786</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3287</v>
       </c>
       <c r="AD9" t="s">
         <v>30</v>
       </c>
       <c r="AE9" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>3287</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" t="b">
+      <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>3291</v>
+      <c r="AH9" t="s">
+        <v>3288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>3292</v>
+        <v>3289</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -12145,59 +12099,57 @@
         <v>52628</v>
       </c>
       <c r="U10" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V10" t="n">
         <v>868477</v>
       </c>
       <c r="W10" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.0864245517290426</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0243193337675716</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3291</v>
       </c>
       <c r="AD10" t="s">
         <v>30</v>
       </c>
       <c r="AE10" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>3295</v>
+      <c r="AH10" t="s">
+        <v>3292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>3296</v>
+        <v>3293</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -12251,62 +12203,60 @@
         <v>52628</v>
       </c>
       <c r="U11" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="V11" t="n">
         <v>257024</v>
       </c>
       <c r="W11" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.0497378455668452</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0144832404187758</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3263</v>
       </c>
       <c r="AD11" t="s">
         <v>30</v>
       </c>
       <c r="AE11" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>3263</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" t="b">
+      <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>3297</v>
+      <c r="AH11" t="s">
+        <v>3294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>3298</v>
+        <v>3295</v>
       </c>
       <c r="D12" t="s">
-        <v>3299</v>
+        <v>3296</v>
       </c>
       <c r="E12" t="n">
         <v>23241</v>
@@ -12357,59 +12307,57 @@
         <v>36697</v>
       </c>
       <c r="U12" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V12" t="n">
         <v>645950</v>
       </c>
       <c r="W12" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.0627032739545255</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0175300373830452</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3291</v>
       </c>
       <c r="AD12" t="s">
         <v>30</v>
       </c>
       <c r="AE12" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH12" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" t="b">
+      <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>3300</v>
+      <c r="AH12" t="s">
+        <v>3297</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>3301</v>
+        <v>3298</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -12463,59 +12411,57 @@
         <v>77001</v>
       </c>
       <c r="U13" t="s">
-        <v>3302</v>
+        <v>3299</v>
       </c>
       <c r="V13" t="n">
         <v>824059</v>
       </c>
       <c r="W13" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.201310453233041</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0589207910094739</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3300</v>
       </c>
       <c r="AD13" t="s">
         <v>30</v>
       </c>
       <c r="AE13" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" t="b">
+      <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>3304</v>
+      <c r="AH13" t="s">
+        <v>3301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>3305</v>
+        <v>3302</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -12569,59 +12515,57 @@
         <v>77001</v>
       </c>
       <c r="U14" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="V14" t="n">
         <v>751961</v>
       </c>
       <c r="W14" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.0939815317243703</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0267371178132133</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3278</v>
       </c>
       <c r="AD14" t="s">
         <v>30</v>
       </c>
       <c r="AE14" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AH14" t="n">
+        <v>3278</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" t="b">
+      <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>3306</v>
+      <c r="AH14" t="s">
+        <v>3303</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>3307</v>
+        <v>3304</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
@@ -12675,59 +12619,57 @@
         <v>52628</v>
       </c>
       <c r="U15" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="V15" t="n">
         <v>37053</v>
       </c>
       <c r="W15" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.101467897217667</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0295204098436051</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3263</v>
       </c>
       <c r="AD15" t="s">
         <v>30</v>
       </c>
       <c r="AE15" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>3263</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>3308</v>
+      <c r="AH15" t="s">
+        <v>3305</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>3309</v>
+        <v>3306</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
@@ -12781,62 +12723,60 @@
         <v>52628</v>
       </c>
       <c r="U16" t="s">
-        <v>3310</v>
+        <v>3307</v>
       </c>
       <c r="V16" t="n">
         <v>117992</v>
       </c>
       <c r="W16" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.15540697893993</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0459462500690984</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3308</v>
       </c>
       <c r="AD16" t="s">
         <v>30</v>
       </c>
       <c r="AE16" t="s">
-        <v>3311</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3311</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>3308</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>3312</v>
+      <c r="AH16" t="s">
+        <v>3309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>3313</v>
+        <v>3310</v>
       </c>
       <c r="D17" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="E17" t="n">
         <v>39867</v>
@@ -12887,59 +12827,57 @@
         <v>48790</v>
       </c>
       <c r="U17" t="s">
-        <v>3302</v>
+        <v>3299</v>
       </c>
       <c r="V17" t="n">
         <v>1057455</v>
       </c>
       <c r="W17" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.0562028772949214</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.0167696748262664</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3300</v>
       </c>
       <c r="AD17" t="s">
         <v>30</v>
       </c>
       <c r="AE17" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" t="b">
+      <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>3315</v>
+      <c r="AH17" t="s">
+        <v>3312</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>3316</v>
+        <v>3313</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
@@ -12993,62 +12931,60 @@
         <v>52628</v>
       </c>
       <c r="U18" t="s">
-        <v>3259</v>
+        <v>3256</v>
       </c>
       <c r="V18" t="n">
         <v>162479</v>
       </c>
       <c r="W18" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.0675414445213979</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0207707454583242</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3259</v>
       </c>
       <c r="AD18" t="s">
         <v>30</v>
       </c>
       <c r="AE18" t="s">
-        <v>3262</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3262</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3259</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" t="b">
+      <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>3316</v>
+      <c r="AH18" t="s">
+        <v>3313</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>3317</v>
+        <v>3314</v>
       </c>
       <c r="D19" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="E19" t="n">
         <v>36697</v>
@@ -13099,59 +13035,57 @@
         <v>48790</v>
       </c>
       <c r="U19" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V19" t="n">
         <v>246990</v>
       </c>
       <c r="W19" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.11371472802983</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.035034881527667</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3291</v>
       </c>
       <c r="AD19" t="s">
         <v>30</v>
       </c>
       <c r="AE19" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>3318</v>
+      <c r="AH19" t="s">
+        <v>3315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>3319</v>
+        <v>3316</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -13205,62 +13139,60 @@
         <v>77001</v>
       </c>
       <c r="U20" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V20" t="n">
         <v>232285</v>
       </c>
       <c r="W20" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-0.0277911267030489</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.00906281327994708</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3272</v>
       </c>
       <c r="AD20" t="s">
         <v>30</v>
       </c>
       <c r="AE20" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>3320</v>
+      <c r="AH20" t="s">
+        <v>3317</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>3321</v>
+        <v>3318</v>
       </c>
       <c r="D21" t="s">
-        <v>3322</v>
+        <v>3319</v>
       </c>
       <c r="E21" t="n">
         <v>860</v>
@@ -13311,62 +13243,60 @@
         <v>12084</v>
       </c>
       <c r="U21" t="s">
-        <v>3323</v>
+        <v>3320</v>
       </c>
       <c r="V21" t="n">
         <v>6401</v>
       </c>
       <c r="W21" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.61356033351864</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.214086546966734</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3321</v>
       </c>
       <c r="AD21" t="s">
         <v>30</v>
       </c>
       <c r="AE21" t="s">
-        <v>3324</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3324</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>3321</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" t="b">
+      <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>3325</v>
+      <c r="AH21" t="s">
+        <v>3322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>3326</v>
+        <v>3323</v>
       </c>
       <c r="D22" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="E22" t="n">
         <v>36697</v>
@@ -13417,59 +13347,57 @@
         <v>48790</v>
       </c>
       <c r="U22" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V22" t="n">
         <v>700594</v>
       </c>
       <c r="W22" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.0311600818507794</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0105660670244751</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3291</v>
       </c>
       <c r="AD22" t="s">
         <v>30</v>
       </c>
       <c r="AE22" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" t="b">
+      <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>3327</v>
+      <c r="AH22" t="s">
+        <v>3324</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>3328</v>
+        <v>3325</v>
       </c>
       <c r="D23" t="s">
         <v>193</v>
@@ -13523,62 +13451,60 @@
         <v>39867</v>
       </c>
       <c r="U23" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V23" t="n">
         <v>39671</v>
       </c>
       <c r="W23" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.0464518493760845</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0168756761895738</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3272</v>
       </c>
       <c r="AD23" t="s">
         <v>30</v>
       </c>
       <c r="AE23" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>3329</v>
+      <c r="AH23" t="s">
+        <v>3326</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>3330</v>
+        <v>3327</v>
       </c>
       <c r="D24" t="s">
-        <v>3322</v>
+        <v>3319</v>
       </c>
       <c r="E24" t="n">
         <v>860</v>
@@ -13629,62 +13555,60 @@
         <v>12084</v>
       </c>
       <c r="U24" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="V24" t="n">
         <v>570649</v>
       </c>
       <c r="W24" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.152354580522292</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.0503053653641155</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3329</v>
       </c>
       <c r="AD24" t="s">
         <v>30</v>
       </c>
       <c r="AE24" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>3329</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" t="b">
+      <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>3333</v>
+      <c r="AH24" t="s">
+        <v>3330</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>3334</v>
+        <v>3331</v>
       </c>
       <c r="D25" t="s">
-        <v>3273</v>
+        <v>3270</v>
       </c>
       <c r="E25" t="n">
         <v>39867</v>
@@ -13735,59 +13659,57 @@
         <v>80882</v>
       </c>
       <c r="U25" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="V25" t="n">
         <v>162768</v>
       </c>
       <c r="W25" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.0823311317225019</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0268149881369901</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>3263</v>
       </c>
       <c r="AD25" t="s">
         <v>30</v>
       </c>
       <c r="AE25" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>3263</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" t="b">
+      <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="s">
-        <v>3335</v>
+      <c r="AH25" t="s">
+        <v>3332</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>3336</v>
+        <v>3333</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
@@ -13841,59 +13763,57 @@
         <v>52628</v>
       </c>
       <c r="U26" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V26" t="n">
         <v>297553</v>
       </c>
       <c r="W26" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.0650208105790152</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0270182160127115</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>3291</v>
       </c>
       <c r="AD26" t="s">
         <v>30</v>
       </c>
       <c r="AE26" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>3337</v>
+        <v>3291</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>3334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>3338</v>
+        <v>3335</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -13947,59 +13867,57 @@
         <v>52628</v>
       </c>
       <c r="U27" t="s">
-        <v>3302</v>
+        <v>3299</v>
       </c>
       <c r="V27" t="n">
         <v>672186</v>
       </c>
       <c r="W27" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.0926160856405786</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0318138055201039</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>3300</v>
       </c>
       <c r="AD27" t="s">
         <v>30</v>
       </c>
       <c r="AE27" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>3339</v>
+      <c r="AH27" t="s">
+        <v>3336</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B28" t="s">
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>3340</v>
+        <v>3337</v>
       </c>
       <c r="D28" t="s">
         <v>193</v>
@@ -14053,59 +13971,57 @@
         <v>39867</v>
       </c>
       <c r="U28" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="V28" t="n">
         <v>411569</v>
       </c>
       <c r="W28" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z28" t="n">
         <v>-0.0826349432380453</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0297039542541449</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>3278</v>
       </c>
       <c r="AD28" t="s">
         <v>30</v>
       </c>
       <c r="AE28" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AH28" t="n">
+        <v>3278</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" t="b">
+      <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>3341</v>
+      <c r="AH28" t="s">
+        <v>3338</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>3342</v>
+        <v>3339</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -14159,62 +14075,60 @@
         <v>52628</v>
       </c>
       <c r="U29" t="s">
-        <v>3289</v>
+        <v>3286</v>
       </c>
       <c r="V29" t="n">
         <v>900150</v>
       </c>
       <c r="W29" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z29" t="n">
         <v>-0.0384934568473152</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0137281718015965</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>3287</v>
       </c>
       <c r="AD29" t="s">
         <v>30</v>
       </c>
       <c r="AE29" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AH29" t="n">
+        <v>3287</v>
+      </c>
+      <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" t="b">
+      <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>3343</v>
+      <c r="AH29" t="s">
+        <v>3340</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B30" t="s">
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>3344</v>
+        <v>3341</v>
       </c>
       <c r="D30" t="s">
-        <v>3322</v>
+        <v>3319</v>
       </c>
       <c r="E30" t="n">
         <v>860</v>
@@ -14265,59 +14179,57 @@
         <v>12084</v>
       </c>
       <c r="U30" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V30" t="n">
         <v>550464</v>
       </c>
       <c r="W30" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z30" t="n">
         <v>-0.0983956168103903</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0373752684073627</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>3291</v>
       </c>
       <c r="AD30" t="s">
         <v>30</v>
       </c>
       <c r="AE30" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH30" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" t="b">
+      <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>3345</v>
+      <c r="AH30" t="s">
+        <v>3342</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>3346</v>
+        <v>3343</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -14371,59 +14283,57 @@
         <v>77001</v>
       </c>
       <c r="U31" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V31" t="n">
         <v>415681</v>
       </c>
       <c r="W31" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z31" t="n">
         <v>-0.0955169591481956</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0344360327118955</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>3272</v>
       </c>
       <c r="AD31" t="s">
         <v>30</v>
       </c>
       <c r="AE31" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" t="b">
+      <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>3347</v>
+      <c r="AH31" t="s">
+        <v>3344</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>3348</v>
+        <v>3345</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -14477,62 +14387,60 @@
         <v>52628</v>
       </c>
       <c r="U32" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V32" t="n">
         <v>809997</v>
       </c>
       <c r="W32" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB32" t="n">
+      <c r="Y32" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.124587281321321</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AA32" t="n">
         <v>0.0435811520157331</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>3272</v>
       </c>
       <c r="AD32" t="s">
         <v>30</v>
       </c>
       <c r="AE32" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH32" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" t="b">
+      <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>3349</v>
+      <c r="AH32" t="s">
+        <v>3346</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>3350</v>
+        <v>3347</v>
       </c>
       <c r="D33" t="s">
-        <v>3273</v>
+        <v>3270</v>
       </c>
       <c r="E33" t="n">
         <v>77001</v>
@@ -14583,59 +14491,57 @@
         <v>80882</v>
       </c>
       <c r="U33" t="s">
-        <v>3259</v>
+        <v>3256</v>
       </c>
       <c r="V33" t="n">
         <v>177365</v>
       </c>
       <c r="W33" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z33" t="n">
         <v>-0.0269220123894415</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
         <v>0.0114678901666434</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>3259</v>
       </c>
       <c r="AD33" t="s">
         <v>30</v>
       </c>
       <c r="AE33" t="s">
-        <v>3262</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>3262</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>3351</v>
+        <v>3259</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>3348</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>3352</v>
+        <v>3349</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -14689,59 +14595,57 @@
         <v>77001</v>
       </c>
       <c r="U34" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V34" t="n">
         <v>368781</v>
       </c>
       <c r="W34" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="Y34" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z34" t="n">
         <v>-0.0264147715829103</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>0.0111471678941989</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>3272</v>
       </c>
       <c r="AD34" t="s">
         <v>30</v>
       </c>
       <c r="AE34" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>3353</v>
+        <v>3272</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>3350</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>3354</v>
+        <v>3351</v>
       </c>
       <c r="D35" t="s">
         <v>193</v>
@@ -14795,59 +14699,57 @@
         <v>39867</v>
       </c>
       <c r="U35" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V35" t="n">
         <v>184925</v>
       </c>
       <c r="W35" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB35" t="n">
+      <c r="Y35" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.139448425116425</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>0.0492162775427452</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>3291</v>
       </c>
       <c r="AD35" t="s">
         <v>30</v>
       </c>
       <c r="AE35" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH35" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF35" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" t="b">
+      <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>3355</v>
+      <c r="AH35" t="s">
+        <v>3352</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B36" t="s">
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>3356</v>
+        <v>3353</v>
       </c>
       <c r="D36" t="s">
         <v>193</v>
@@ -14901,27 +14803,31 @@
         <v>39867</v>
       </c>
       <c r="U36" t="s">
-        <v>3284</v>
+        <v>3281</v>
       </c>
       <c r="V36" t="n">
         <v>207877</v>
       </c>
       <c r="W36" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="Y36" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.101000090078314</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>0.0387040309677558</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>45</v>
       </c>
       <c r="AD36" t="s">
         <v>30</v>
@@ -14929,34 +14835,28 @@
       <c r="AE36" t="s">
         <v>45</v>
       </c>
-      <c r="AF36" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH36" t="n">
+      <c r="AF36" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" t="b">
+      <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>3357</v>
+      <c r="AH36" t="s">
+        <v>3354</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>3358</v>
+        <v>3355</v>
       </c>
       <c r="D37" t="s">
-        <v>3299</v>
+        <v>3296</v>
       </c>
       <c r="E37" t="n">
         <v>23241</v>
@@ -15007,59 +14907,57 @@
         <v>36697</v>
       </c>
       <c r="U37" t="s">
-        <v>3289</v>
+        <v>3286</v>
       </c>
       <c r="V37" t="n">
         <v>925721</v>
       </c>
       <c r="W37" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Y37" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.140080942733608</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AA37" t="n">
         <v>0.0501991048523253</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>3287</v>
       </c>
       <c r="AD37" t="s">
         <v>30</v>
       </c>
       <c r="AE37" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AH37" t="n">
+        <v>3287</v>
+      </c>
+      <c r="AF37" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" t="b">
+      <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>3359</v>
+      <c r="AH37" t="s">
+        <v>3356</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>3360</v>
+        <v>3357</v>
       </c>
       <c r="D38" t="s">
         <v>29</v>
@@ -15113,59 +15011,57 @@
         <v>52628</v>
       </c>
       <c r="U38" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V38" t="n">
         <v>673131</v>
       </c>
       <c r="W38" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
-      <c r="Y38"/>
-      <c r="Z38"/>
-      <c r="AA38" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="Y38" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.0445799467585412</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AA38" t="n">
         <v>0.0162739350627652</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>3272</v>
       </c>
       <c r="AD38" t="s">
         <v>30</v>
       </c>
       <c r="AE38" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH38" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" t="b">
+      <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>3361</v>
+      <c r="AH38" t="s">
+        <v>3358</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>3362</v>
+        <v>3359</v>
       </c>
       <c r="D39" t="s">
         <v>29</v>
@@ -15219,59 +15115,57 @@
         <v>52628</v>
       </c>
       <c r="U39" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="V39" t="n">
         <v>149083</v>
       </c>
       <c r="W39" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
-      <c r="Y39"/>
-      <c r="Z39"/>
-      <c r="AA39" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="Y39" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.149025371209915</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AA39" t="n">
         <v>0.0558572655804517</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>3329</v>
       </c>
       <c r="AD39" t="s">
         <v>30</v>
       </c>
       <c r="AE39" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AH39" t="n">
+        <v>3329</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" t="b">
+      <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>3363</v>
+      <c r="AH39" t="s">
+        <v>3360</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B40" t="s">
         <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>3364</v>
+        <v>3361</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -15325,59 +15219,57 @@
         <v>52628</v>
       </c>
       <c r="U40" t="s">
-        <v>3310</v>
+        <v>3307</v>
       </c>
       <c r="V40" t="n">
         <v>186397</v>
       </c>
       <c r="W40" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
       </c>
-      <c r="Y40"/>
-      <c r="Z40"/>
-      <c r="AA40" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="Y40" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.0547892883755027</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AA40" t="n">
         <v>0.0196976203895797</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>3308</v>
       </c>
       <c r="AD40" t="s">
         <v>30</v>
       </c>
       <c r="AE40" t="s">
-        <v>3311</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>3311</v>
-      </c>
-      <c r="AH40" t="n">
+        <v>3308</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" t="b">
+      <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>3365</v>
+      <c r="AH40" t="s">
+        <v>3362</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>3366</v>
+        <v>3363</v>
       </c>
       <c r="D41" t="s">
         <v>193</v>
@@ -15431,59 +15323,57 @@
         <v>39867</v>
       </c>
       <c r="U41" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="V41" t="n">
         <v>1393201</v>
       </c>
       <c r="W41" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
       </c>
-      <c r="Y41"/>
-      <c r="Z41"/>
-      <c r="AA41" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="Y41" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.116799777603019</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AA41" t="n">
         <v>0.0507738336003275</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>3329</v>
       </c>
       <c r="AD41" t="s">
         <v>30</v>
       </c>
       <c r="AE41" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AF41" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>3367</v>
+        <v>3329</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>3364</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B42" t="s">
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>3368</v>
+        <v>3365</v>
       </c>
       <c r="D42" t="s">
         <v>22</v>
@@ -15537,59 +15427,57 @@
         <v>77001</v>
       </c>
       <c r="U42" t="s">
-        <v>3269</v>
+        <v>3266</v>
       </c>
       <c r="V42" t="n">
         <v>398464</v>
       </c>
       <c r="W42" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
       </c>
-      <c r="Y42"/>
-      <c r="Z42"/>
-      <c r="AA42" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB42" t="n">
+      <c r="Y42" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.15316564940021</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AA42" t="n">
         <v>0.0600091779199681</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>3267</v>
       </c>
       <c r="AD42" t="s">
         <v>30</v>
       </c>
       <c r="AE42" t="s">
-        <v>3270</v>
-      </c>
-      <c r="AF42" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>3270</v>
-      </c>
-      <c r="AH42" t="n">
+        <v>3267</v>
+      </c>
+      <c r="AF42" t="n">
         <v>0</v>
       </c>
-      <c r="AI42" t="b">
+      <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="s">
-        <v>3369</v>
+      <c r="AH42" t="s">
+        <v>3366</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>3370</v>
+        <v>3367</v>
       </c>
       <c r="D43" t="s">
         <v>193</v>
@@ -15643,59 +15531,57 @@
         <v>39867</v>
       </c>
       <c r="U43" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V43" t="n">
         <v>131729</v>
       </c>
       <c r="W43" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
       </c>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AA43" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="Y43" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.128029645472287</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AA43" t="n">
         <v>0.0498144501892095</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>3272</v>
       </c>
       <c r="AD43" t="s">
         <v>30</v>
       </c>
       <c r="AE43" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF43" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH43" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF43" t="n">
         <v>0</v>
       </c>
-      <c r="AI43" t="b">
+      <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="s">
-        <v>3371</v>
+      <c r="AH43" t="s">
+        <v>3368</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>3372</v>
+        <v>3369</v>
       </c>
       <c r="D44" t="s">
         <v>22</v>
@@ -15749,59 +15635,57 @@
         <v>77001</v>
       </c>
       <c r="U44" t="s">
-        <v>3289</v>
+        <v>3286</v>
       </c>
       <c r="V44" t="n">
         <v>444686</v>
       </c>
       <c r="W44" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
       </c>
-      <c r="Y44"/>
-      <c r="Z44"/>
-      <c r="AA44" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="Y44" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.0279519609714869</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AA44" t="n">
         <v>0.0109413632502198</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>3287</v>
       </c>
       <c r="AD44" t="s">
         <v>30</v>
       </c>
       <c r="AE44" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AH44" t="n">
+        <v>3287</v>
+      </c>
+      <c r="AF44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" t="b">
+      <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="s">
-        <v>3373</v>
+      <c r="AH44" t="s">
+        <v>3370</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>3374</v>
+        <v>3371</v>
       </c>
       <c r="D45" t="s">
         <v>29</v>
@@ -15855,59 +15739,57 @@
         <v>52628</v>
       </c>
       <c r="U45" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V45" t="n">
         <v>276042</v>
       </c>
       <c r="W45" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
       </c>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="Y45" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.114732008664954</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AA45" t="n">
         <v>0.0503370514804567</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>3291</v>
       </c>
       <c r="AD45" t="s">
         <v>30</v>
       </c>
       <c r="AE45" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF45" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH45" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF45" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" t="b">
+      <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="s">
-        <v>3375</v>
+      <c r="AH45" t="s">
+        <v>3372</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>3376</v>
+        <v>3373</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -15961,59 +15843,57 @@
         <v>52628</v>
       </c>
       <c r="U46" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V46" t="n">
         <v>139500</v>
       </c>
       <c r="W46" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
       </c>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AA46" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB46" t="n">
+      <c r="Y46" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.138951903886657</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AA46" t="n">
         <v>0.0527409825590306</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>3291</v>
       </c>
       <c r="AD46" t="s">
         <v>30</v>
       </c>
       <c r="AE46" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH46" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF46" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" t="b">
+      <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="s">
-        <v>3377</v>
+      <c r="AH46" t="s">
+        <v>3374</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>3378</v>
+        <v>3375</v>
       </c>
       <c r="D47" t="s">
         <v>29</v>
@@ -16067,59 +15947,57 @@
         <v>52628</v>
       </c>
       <c r="U47" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="V47" t="n">
         <v>840475</v>
       </c>
       <c r="W47" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
       </c>
-      <c r="Y47"/>
-      <c r="Z47"/>
-      <c r="AA47" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB47" t="n">
+      <c r="Y47" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z47" t="n">
         <v>0.10154714859099</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AA47" t="n">
         <v>0.0387516978563699</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>3329</v>
       </c>
       <c r="AD47" t="s">
         <v>30</v>
       </c>
       <c r="AE47" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AH47" t="n">
+        <v>3329</v>
+      </c>
+      <c r="AF47" t="n">
         <v>0</v>
       </c>
-      <c r="AI47" t="b">
+      <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AJ47" t="s">
-        <v>3379</v>
+      <c r="AH47" t="s">
+        <v>3376</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>3380</v>
+        <v>3377</v>
       </c>
       <c r="D48" t="s">
         <v>22</v>
@@ -16173,59 +16051,57 @@
         <v>77001</v>
       </c>
       <c r="U48" t="s">
-        <v>3302</v>
+        <v>3299</v>
       </c>
       <c r="V48" t="n">
         <v>912824</v>
       </c>
       <c r="W48" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X48" t="b">
         <v>1</v>
       </c>
-      <c r="Y48"/>
-      <c r="Z48"/>
-      <c r="AA48" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="Y48" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z48" t="n">
         <v>-0.0474908022787406</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AA48" t="n">
         <v>0.0191553835131715</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>3300</v>
       </c>
       <c r="AD48" t="s">
         <v>30</v>
       </c>
       <c r="AE48" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AF48" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG48" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AH48" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AF48" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" t="b">
+      <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="s">
-        <v>3381</v>
+      <c r="AH48" t="s">
+        <v>3378</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B49" t="s">
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>3382</v>
+        <v>3379</v>
       </c>
       <c r="D49" t="s">
         <v>29</v>
@@ -16279,62 +16155,60 @@
         <v>52628</v>
       </c>
       <c r="U49" t="s">
-        <v>3323</v>
+        <v>3320</v>
       </c>
       <c r="V49" t="n">
         <v>159438</v>
       </c>
       <c r="W49" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
-      <c r="Y49"/>
-      <c r="Z49"/>
-      <c r="AA49" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB49" t="n">
+      <c r="Y49" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z49" t="n">
         <v>-0.140679785082809</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AA49" t="n">
         <v>0.0550432294759719</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>3321</v>
       </c>
       <c r="AD49" t="s">
         <v>30</v>
       </c>
       <c r="AE49" t="s">
-        <v>3324</v>
-      </c>
-      <c r="AF49" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG49" t="s">
-        <v>3324</v>
-      </c>
-      <c r="AH49" t="n">
+        <v>3321</v>
+      </c>
+      <c r="AF49" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" t="b">
+      <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="s">
-        <v>3383</v>
+      <c r="AH49" t="s">
+        <v>3380</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B50" t="s">
         <v>19</v>
       </c>
       <c r="C50" t="s">
-        <v>3384</v>
+        <v>3381</v>
       </c>
       <c r="D50" t="s">
-        <v>3322</v>
+        <v>3319</v>
       </c>
       <c r="E50" t="n">
         <v>860</v>
@@ -16385,59 +16259,57 @@
         <v>12084</v>
       </c>
       <c r="U50" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="V50" t="n">
         <v>267174</v>
       </c>
       <c r="W50" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
       </c>
-      <c r="Y50"/>
-      <c r="Z50"/>
-      <c r="AA50" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="Y50" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z50" t="n">
         <v>-0.08522134917642</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AA50" t="n">
         <v>0.0326420512608436</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>3278</v>
       </c>
       <c r="AD50" t="s">
         <v>30</v>
       </c>
       <c r="AE50" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG50" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AH50" t="n">
+        <v>3278</v>
+      </c>
+      <c r="AF50" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" t="b">
+      <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="s">
-        <v>3385</v>
+      <c r="AH50" t="s">
+        <v>3382</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B51" t="s">
         <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>3386</v>
+        <v>3383</v>
       </c>
       <c r="D51" t="s">
         <v>22</v>
@@ -16491,59 +16363,57 @@
         <v>77001</v>
       </c>
       <c r="U51" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="V51" t="n">
         <v>119989</v>
       </c>
       <c r="W51" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
       </c>
-      <c r="Y51"/>
-      <c r="Z51"/>
-      <c r="AA51" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="Y51" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.0717942488317671</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AA51" t="n">
         <v>0.0311494161406157</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>3278</v>
       </c>
       <c r="AD51" t="s">
         <v>30</v>
       </c>
       <c r="AE51" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AF51" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG51" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AH51" t="n">
+        <v>3278</v>
+      </c>
+      <c r="AF51" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" t="b">
+      <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="s">
-        <v>3387</v>
+      <c r="AH51" t="s">
+        <v>3384</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
       </c>
       <c r="C52" t="s">
-        <v>3388</v>
+        <v>3385</v>
       </c>
       <c r="D52" t="s">
         <v>193</v>
@@ -16597,62 +16467,60 @@
         <v>39867</v>
       </c>
       <c r="U52" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V52" t="n">
         <v>74119</v>
       </c>
       <c r="W52" t="s">
-        <v>3285</v>
+        <v>3282</v>
       </c>
       <c r="X52" t="b">
         <v>1</v>
       </c>
-      <c r="Y52"/>
-      <c r="Z52"/>
-      <c r="AA52" t="s">
-        <v>3286</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="Y52" t="s">
+        <v>3283</v>
+      </c>
+      <c r="Z52" t="n">
         <v>-0.0582956732024312</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AA52" t="n">
         <v>0.0221049866827263</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>3291</v>
       </c>
       <c r="AD52" t="s">
         <v>30</v>
       </c>
       <c r="AE52" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF52" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG52" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH52" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF52" t="n">
         <v>0</v>
       </c>
-      <c r="AI52" t="b">
+      <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AJ52" t="s">
-        <v>3389</v>
+      <c r="AH52" t="s">
+        <v>3386</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B53" t="s">
         <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>3390</v>
+        <v>3387</v>
       </c>
       <c r="D53" t="s">
-        <v>3391</v>
+        <v>3388</v>
       </c>
       <c r="E53" t="n">
         <v>79814</v>
@@ -16703,62 +16571,60 @@
         <v>85896</v>
       </c>
       <c r="U53" t="s">
-        <v>3274</v>
+        <v>3271</v>
       </c>
       <c r="V53" t="n">
         <v>1006378</v>
       </c>
       <c r="W53" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X53" t="b">
         <v>1</v>
       </c>
-      <c r="Y53"/>
-      <c r="Z53"/>
-      <c r="AA53" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB53" t="n">
+      <c r="Y53" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.122267534820055</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AA53" t="n">
         <v>0.0496075217191251</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>3272</v>
       </c>
       <c r="AD53" t="s">
         <v>30</v>
       </c>
       <c r="AE53" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG53" t="s">
-        <v>3275</v>
-      </c>
-      <c r="AH53" t="n">
+        <v>3272</v>
+      </c>
+      <c r="AF53" t="n">
         <v>0</v>
       </c>
-      <c r="AI53" t="b">
+      <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AJ53" t="s">
-        <v>3392</v>
+      <c r="AH53" t="s">
+        <v>3389</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
       </c>
       <c r="C54" t="s">
-        <v>3393</v>
+        <v>3390</v>
       </c>
       <c r="D54" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="E54" t="n">
         <v>12084</v>
@@ -16809,62 +16675,60 @@
         <v>48790</v>
       </c>
       <c r="U54" t="s">
-        <v>3289</v>
+        <v>3286</v>
       </c>
       <c r="V54" t="n">
         <v>921416</v>
       </c>
       <c r="W54" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X54" t="b">
         <v>1</v>
       </c>
-      <c r="Y54"/>
-      <c r="Z54"/>
-      <c r="AA54" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB54" t="n">
+      <c r="Y54" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.096990515736282</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AA54" t="n">
         <v>0.0409715973737959</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>3287</v>
       </c>
       <c r="AD54" t="s">
         <v>30</v>
       </c>
       <c r="AE54" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AF54" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG54" t="s">
-        <v>3290</v>
-      </c>
-      <c r="AH54" t="n">
+        <v>3287</v>
+      </c>
+      <c r="AF54" t="n">
         <v>0</v>
       </c>
-      <c r="AI54" t="b">
+      <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AJ54" t="s">
-        <v>3394</v>
+      <c r="AH54" t="s">
+        <v>3391</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
       </c>
       <c r="C55" t="s">
-        <v>3395</v>
+        <v>3392</v>
       </c>
       <c r="D55" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="E55" t="n">
         <v>860</v>
@@ -16915,59 +16779,57 @@
         <v>48790</v>
       </c>
       <c r="U55" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="V55" t="n">
         <v>143869</v>
       </c>
       <c r="W55" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X55" t="b">
         <v>1</v>
       </c>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AA55" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="Y55" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.0885798395230417</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AA55" t="n">
         <v>0.0394902655384902</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>3263</v>
       </c>
       <c r="AD55" t="s">
         <v>30</v>
       </c>
       <c r="AE55" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG55" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AH55" t="n">
+        <v>3263</v>
+      </c>
+      <c r="AF55" t="n">
         <v>0</v>
       </c>
-      <c r="AI55" t="b">
+      <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AJ55" t="s">
-        <v>3396</v>
+      <c r="AH55" t="s">
+        <v>3393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
       </c>
       <c r="C56" t="s">
-        <v>3397</v>
+        <v>3394</v>
       </c>
       <c r="D56" t="s">
         <v>22</v>
@@ -17021,59 +16883,57 @@
         <v>77001</v>
       </c>
       <c r="U56" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="V56" t="n">
         <v>845818</v>
       </c>
       <c r="W56" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X56" t="b">
         <v>1</v>
       </c>
-      <c r="Y56"/>
-      <c r="Z56"/>
-      <c r="AA56" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB56" t="n">
+      <c r="Y56" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z56" t="n">
         <v>0.131602124733236</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AA56" t="n">
         <v>0.0572919289367495</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>3329</v>
       </c>
       <c r="AD56" t="s">
         <v>30</v>
       </c>
       <c r="AE56" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AF56" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG56" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AH56" t="n">
+        <v>3329</v>
+      </c>
+      <c r="AF56" t="n">
         <v>0</v>
       </c>
-      <c r="AI56" t="b">
+      <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="s">
-        <v>3398</v>
+      <c r="AH56" t="s">
+        <v>3395</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B57" t="s">
         <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>3399</v>
+        <v>3396</v>
       </c>
       <c r="D57" t="s">
         <v>22</v>
@@ -17127,59 +16987,57 @@
         <v>77001</v>
       </c>
       <c r="U57" t="s">
-        <v>3280</v>
+        <v>3277</v>
       </c>
       <c r="V57" t="n">
         <v>272193</v>
       </c>
       <c r="W57" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X57" t="b">
         <v>1</v>
       </c>
-      <c r="Y57"/>
-      <c r="Z57"/>
-      <c r="AA57" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB57" t="n">
+      <c r="Y57" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z57" t="n">
         <v>0.0654154924764921</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AA57" t="n">
         <v>0.0318623472756603</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>3278</v>
       </c>
       <c r="AD57" t="s">
         <v>30</v>
       </c>
       <c r="AE57" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AF57" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG57" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ57" t="s">
-        <v>3400</v>
+        <v>3278</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>3397</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>3401</v>
+        <v>3398</v>
       </c>
       <c r="D58" t="s">
         <v>22</v>
@@ -17233,62 +17091,60 @@
         <v>77001</v>
       </c>
       <c r="U58" t="s">
-        <v>3293</v>
+        <v>3290</v>
       </c>
       <c r="V58" t="n">
         <v>535700</v>
       </c>
       <c r="W58" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X58" t="b">
         <v>1</v>
       </c>
-      <c r="Y58"/>
-      <c r="Z58"/>
-      <c r="AA58" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB58" t="n">
+      <c r="Y58" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z58" t="n">
         <v>0.13052358324519</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AA58" t="n">
         <v>0.0554344044991441</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>3291</v>
       </c>
       <c r="AD58" t="s">
         <v>30</v>
       </c>
       <c r="AE58" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AF58" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG58" t="s">
-        <v>3294</v>
-      </c>
-      <c r="AH58" t="n">
+        <v>3291</v>
+      </c>
+      <c r="AF58" t="n">
         <v>0</v>
       </c>
-      <c r="AI58" t="b">
+      <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="s">
-        <v>3402</v>
+      <c r="AH58" t="s">
+        <v>3399</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B59" t="s">
         <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>3403</v>
+        <v>3400</v>
       </c>
       <c r="D59" t="s">
-        <v>3404</v>
+        <v>3401</v>
       </c>
       <c r="E59" t="n">
         <v>39867</v>
@@ -17339,59 +17195,57 @@
         <v>78708</v>
       </c>
       <c r="U59" t="s">
-        <v>3405</v>
+        <v>3402</v>
       </c>
       <c r="V59" t="n">
         <v>213312</v>
       </c>
       <c r="W59" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X59" t="b">
         <v>1</v>
       </c>
-      <c r="Y59"/>
-      <c r="Z59"/>
-      <c r="AA59" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB59" t="n">
+      <c r="Y59" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.0704029375416636</v>
       </c>
-      <c r="AC59" t="n">
+      <c r="AA59" t="n">
         <v>0.0320583128196263</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>3403</v>
       </c>
       <c r="AD59" t="s">
         <v>30</v>
       </c>
       <c r="AE59" t="s">
-        <v>3406</v>
-      </c>
-      <c r="AF59" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>3406</v>
-      </c>
-      <c r="AH59" t="n">
+        <v>3403</v>
+      </c>
+      <c r="AF59" t="n">
         <v>0</v>
       </c>
-      <c r="AI59" t="b">
+      <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="s">
-        <v>3407</v>
+      <c r="AH59" t="s">
+        <v>3404</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>3408</v>
+        <v>3405</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -17445,62 +17299,60 @@
         <v>77001</v>
       </c>
       <c r="U60" t="s">
-        <v>3331</v>
+        <v>3328</v>
       </c>
       <c r="V60" t="n">
         <v>755628</v>
       </c>
       <c r="W60" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X60" t="b">
         <v>1</v>
       </c>
-      <c r="Y60"/>
-      <c r="Z60"/>
-      <c r="AA60" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB60" t="n">
+      <c r="Y60" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.128017306598502</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AA60" t="n">
         <v>0.0500099961351987</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>3329</v>
       </c>
       <c r="AD60" t="s">
         <v>30</v>
       </c>
       <c r="AE60" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AF60" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG60" t="s">
-        <v>3332</v>
-      </c>
-      <c r="AH60" t="n">
+        <v>3329</v>
+      </c>
+      <c r="AF60" t="n">
         <v>0</v>
       </c>
-      <c r="AI60" t="b">
+      <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="s">
-        <v>3409</v>
+      <c r="AH60" t="s">
+        <v>3406</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B61" t="s">
         <v>19</v>
       </c>
       <c r="C61" t="s">
-        <v>3410</v>
+        <v>3407</v>
       </c>
       <c r="D61" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="E61" t="n">
         <v>48790</v>
@@ -17551,59 +17403,57 @@
         <v>48790</v>
       </c>
       <c r="U61" t="s">
-        <v>3302</v>
+        <v>3299</v>
       </c>
       <c r="V61" t="n">
         <v>1048678</v>
       </c>
       <c r="W61" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X61" t="b">
         <v>1</v>
       </c>
-      <c r="Y61"/>
-      <c r="Z61"/>
-      <c r="AA61" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB61" t="n">
+      <c r="Y61" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z61" t="n">
         <v>-0.0451472395314542</v>
       </c>
-      <c r="AC61" t="n">
+      <c r="AA61" t="n">
         <v>0.0222751267344268</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>3300</v>
       </c>
       <c r="AD61" t="s">
         <v>30</v>
       </c>
       <c r="AE61" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AF61" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>3303</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>3411</v>
+        <v>3300</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>3408</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>3257</v>
+        <v>3254</v>
       </c>
       <c r="B62" t="s">
         <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>3412</v>
+        <v>3409</v>
       </c>
       <c r="D62" t="s">
         <v>29</v>
@@ -17657,48 +17507,46 @@
         <v>52628</v>
       </c>
       <c r="U62" t="s">
-        <v>3265</v>
+        <v>3262</v>
       </c>
       <c r="V62" t="n">
         <v>491126</v>
       </c>
       <c r="W62" t="s">
-        <v>3260</v>
+        <v>3257</v>
       </c>
       <c r="X62" t="b">
         <v>1</v>
       </c>
-      <c r="Y62"/>
-      <c r="Z62"/>
-      <c r="AA62" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AB62" t="n">
+      <c r="Y62" t="s">
+        <v>3258</v>
+      </c>
+      <c r="Z62" t="n">
         <v>-0.0718423399458458</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AA62" t="n">
         <v>0.0286594975048024</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>3263</v>
       </c>
       <c r="AD62" t="s">
         <v>30</v>
       </c>
       <c r="AE62" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AF62" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG62" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AH62" t="n">
+        <v>3263</v>
+      </c>
+      <c r="AF62" t="n">
         <v>0</v>
       </c>
-      <c r="AI62" t="b">
+      <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="s">
-        <v>3413</v>
+      <c r="AH62" t="s">
+        <v>3410</v>
       </c>
     </row>
   </sheetData>
@@ -17777,37 +17625,28 @@
         <v>3244</v>
       </c>
       <c r="V1" t="s">
-        <v>3414</v>
+        <v>142</v>
       </c>
       <c r="W1" t="s">
-        <v>3415</v>
+        <v>3247</v>
       </c>
       <c r="X1" t="s">
-        <v>3416</v>
+        <v>3248</v>
       </c>
       <c r="Y1" t="s">
-        <v>3417</v>
+        <v>3249</v>
       </c>
       <c r="Z1" t="s">
-        <v>3418</v>
+        <v>28</v>
       </c>
       <c r="AA1" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="AB1" t="s">
-        <v>3252</v>
+        <v>3411</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3253</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3419</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3256</v>
       </c>
     </row>
     <row r="2">
@@ -17815,10 +17654,10 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>3420</v>
+        <v>3412</v>
       </c>
       <c r="C2" t="s">
-        <v>3299</v>
+        <v>3296</v>
       </c>
       <c r="D2" t="n">
         <v>36697</v>
@@ -17875,37 +17714,28 @@
         <v>36579</v>
       </c>
       <c r="V2" t="n">
-        <v>-18.9121323105427</v>
+        <v>-0.929731188975305</v>
       </c>
       <c r="W2" t="n">
-        <v>-8.26206250506475</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-7.96834714345209</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-6.82712192417033</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-10.3563025266318</v>
+        <v>0.079304005206309</v>
+      </c>
+      <c r="X2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>30</v>
       </c>
       <c r="AA2" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" t="s">
-        <v>30</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3421</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="3">
@@ -17913,7 +17743,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>3422</v>
+        <v>3414</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -17973,37 +17803,28 @@
         <v>63810</v>
       </c>
       <c r="V3" t="n">
-        <v>-10.1526515249361</v>
+        <v>-0.322854933506615</v>
       </c>
       <c r="W3" t="n">
-        <v>-7.03099870725718</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-3.27121333416951</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-9.85770716855852</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-6.83932641112269</v>
+        <v>0.0410366324679392</v>
+      </c>
+      <c r="X3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>30</v>
       </c>
       <c r="AA3" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" t="s">
-        <v>30</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3423</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="4">
@@ -18011,10 +17832,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>3424</v>
+        <v>3416</v>
       </c>
       <c r="C4" t="s">
-        <v>3425</v>
+        <v>3417</v>
       </c>
       <c r="D4" t="n">
         <v>860</v>
@@ -18071,37 +17892,28 @@
         <v>26707</v>
       </c>
       <c r="V4" t="n">
-        <v>4.41163143150798</v>
+        <v>0.647062236870876</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0114061188893</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.96143827605971</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.64573984152984</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.42395253329681</v>
+        <v>0.171671256397618</v>
+      </c>
+      <c r="X4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>30</v>
       </c>
       <c r="AA4" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" t="s">
-        <v>30</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3426</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="5">
@@ -18109,10 +17921,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>3427</v>
+        <v>3419</v>
       </c>
       <c r="C5" t="s">
-        <v>3425</v>
+        <v>3417</v>
       </c>
       <c r="D5" t="n">
         <v>23241</v>
@@ -18169,37 +17981,28 @@
         <v>25215</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.98260200720699</v>
+        <v>-0.162540780099907</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.01010952867082</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2.21531466855123</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.202168201292081</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-1.80773670650903</v>
+        <v>0.0486521583882997</v>
+      </c>
+      <c r="X5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>30</v>
       </c>
       <c r="AA5" t="s">
         <v>30</v>
       </c>
-      <c r="AB5" t="s">
-        <v>30</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3428</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="6">
@@ -18207,7 +18010,7 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>3429</v>
+        <v>3421</v>
       </c>
       <c r="C6" t="s">
         <v>193</v>
@@ -18267,37 +18070,28 @@
         <v>42303</v>
       </c>
       <c r="V6" t="n">
-        <v>6.06176155283538</v>
+        <v>0.170239884235441</v>
       </c>
       <c r="W6" t="n">
-        <v>3.34463308961932</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.806816640197282</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.72116363785156</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.4973886252651</v>
+        <v>0.0528690929307562</v>
+      </c>
+      <c r="X6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>30</v>
       </c>
       <c r="AA6" t="s">
         <v>30</v>
       </c>
-      <c r="AB6" t="s">
-        <v>30</v>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3430</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="7">
@@ -18365,36 +18159,27 @@
         <v>70614</v>
       </c>
       <c r="V7" t="n">
-        <v>2.79689444455809</v>
+        <v>0.361933866426443</v>
       </c>
       <c r="W7" t="n">
-        <v>2.79810248928111</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.23984677494389</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.66576204408278</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.62269496137947</v>
+        <v>0.124089581042243</v>
+      </c>
+      <c r="X7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>30</v>
       </c>
       <c r="AA7" t="s">
         <v>30</v>
       </c>
-      <c r="AB7" t="s">
-        <v>30</v>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
         <v>119</v>
       </c>
     </row>
@@ -18403,10 +18188,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>3431</v>
+        <v>3423</v>
       </c>
       <c r="C8" t="s">
-        <v>3299</v>
+        <v>3296</v>
       </c>
       <c r="D8" t="n">
         <v>36697</v>
@@ -18463,37 +18248,28 @@
         <v>31886</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6686941600374</v>
+        <v>0.171172873809881</v>
       </c>
       <c r="W8" t="n">
-        <v>4.3351503269683</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.85729424254215</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.504045727487132</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.60229731870134</v>
+        <v>0.074723137073036</v>
+      </c>
+      <c r="X8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>30</v>
       </c>
       <c r="AA8" t="s">
         <v>30</v>
       </c>
-      <c r="AB8" t="s">
-        <v>30</v>
+      <c r="AB8" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3432</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="9">
@@ -18501,10 +18277,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>3433</v>
+        <v>3425</v>
       </c>
       <c r="C9" t="s">
-        <v>3434</v>
+        <v>3426</v>
       </c>
       <c r="D9" t="n">
         <v>48790</v>
@@ -18561,37 +18337,28 @@
         <v>80024</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.68074158922005</v>
+        <v>-0.10699265680742</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.10829969205812</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.31399004236226</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-2.7378054305524</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-2.51761824113839</v>
+        <v>0.0372535908114231</v>
+      </c>
+      <c r="X9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>30</v>
       </c>
       <c r="AA9" t="s">
         <v>30</v>
       </c>
-      <c r="AB9" t="s">
-        <v>30</v>
+      <c r="AB9" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3435</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="10">
@@ -18599,7 +18366,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>3436</v>
+        <v>3428</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
@@ -18659,37 +18426,28 @@
         <v>75821</v>
       </c>
       <c r="V10" t="n">
-        <v>3.45157512767901</v>
+        <v>0.131974844236556</v>
       </c>
       <c r="W10" t="n">
-        <v>1.74241124156366</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.458768259049527</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.50125297159537</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.94001143740361</v>
+        <v>0.0578188966797778</v>
+      </c>
+      <c r="X10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>30</v>
       </c>
       <c r="AA10" t="s">
         <v>30</v>
       </c>
-      <c r="AB10" t="s">
-        <v>30</v>
+      <c r="AB10" t="n">
+        <v>0.00201680672268908</v>
       </c>
       <c r="AC10" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.00201680672268908</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3437</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="11">
@@ -18697,10 +18455,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>3438</v>
+        <v>3430</v>
       </c>
       <c r="C11" t="s">
-        <v>3434</v>
+        <v>3426</v>
       </c>
       <c r="D11" t="n">
         <v>77001</v>
@@ -18757,37 +18515,28 @@
         <v>78746</v>
       </c>
       <c r="V11" t="n">
-        <v>1.93504921286218</v>
+        <v>0.186400033907794</v>
       </c>
       <c r="W11" t="n">
-        <v>2.61572416476391</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.585155247924716</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.369650183573578</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.44102949116437</v>
+        <v>0.103079357225932</v>
+      </c>
+      <c r="X11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>30</v>
       </c>
       <c r="AA11" t="s">
         <v>30</v>
       </c>
-      <c r="AB11" t="s">
-        <v>30</v>
+      <c r="AB11" t="n">
+        <v>0.00309423347398031</v>
       </c>
       <c r="AC11" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.00309423347398031</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3439</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="12">
@@ -18795,10 +18544,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>3440</v>
+        <v>3432</v>
       </c>
       <c r="C12" t="s">
-        <v>3441</v>
+        <v>3433</v>
       </c>
       <c r="D12" t="n">
         <v>36697</v>
@@ -18855,37 +18604,28 @@
         <v>77050</v>
       </c>
       <c r="V12" t="n">
-        <v>4.40610030538855</v>
+        <v>0.199601196252303</v>
       </c>
       <c r="W12" t="n">
-        <v>0.533612812516355</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.39368599434107</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.127515388231262</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.287733970206155</v>
+        <v>0.114314784834407</v>
+      </c>
+      <c r="X12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>30</v>
       </c>
       <c r="AA12" t="s">
         <v>30</v>
       </c>
-      <c r="AB12" t="s">
-        <v>30</v>
+      <c r="AB12" t="n">
+        <v>0.00459459459459459</v>
       </c>
       <c r="AC12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.00459459459459459</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>3442</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="13">
@@ -18893,7 +18633,7 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>3443</v>
+        <v>3435</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -18953,37 +18693,28 @@
         <v>55815</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3510901706173</v>
+        <v>0.171140717286919</v>
       </c>
       <c r="W13" t="n">
-        <v>0.617418313142808</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.91780627613281</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.8342788873655</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.41413976223863</v>
+        <v>0.0976373705595881</v>
+      </c>
+      <c r="X13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>30</v>
       </c>
       <c r="AA13" t="s">
         <v>30</v>
       </c>
-      <c r="AB13" t="s">
-        <v>30</v>
+      <c r="AB13" t="n">
+        <v>0.00645994832041344</v>
       </c>
       <c r="AC13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.00645994832041344</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>3444</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="14">
@@ -19051,36 +18782,27 @@
         <v>39163</v>
       </c>
       <c r="V14" t="n">
-        <v>3.18356161044476</v>
+        <v>0.0923541015115046</v>
       </c>
       <c r="W14" t="n">
-        <v>2.70823952384866</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03688364052743</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-1.24509913318437</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.484815139855409</v>
+        <v>0.0590089571286058</v>
+      </c>
+      <c r="X14" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>30</v>
       </c>
       <c r="AA14" t="s">
         <v>30</v>
       </c>
-      <c r="AB14" t="s">
-        <v>30</v>
+      <c r="AB14" t="n">
+        <v>0.00735614346226333</v>
       </c>
       <c r="AC14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.00735614346226333</v>
-      </c>
-      <c r="AF14" t="s">
         <v>99</v>
       </c>
     </row>
@@ -19089,10 +18811,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>3445</v>
+        <v>3437</v>
       </c>
       <c r="C15" t="s">
-        <v>3314</v>
+        <v>3311</v>
       </c>
       <c r="D15" t="n">
         <v>39867</v>
@@ -19149,37 +18871,28 @@
         <v>48918</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38458457436526</v>
+        <v>0.0740883235169802</v>
       </c>
       <c r="W15" t="n">
-        <v>0.559645248568249</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.62226550534388</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.995185691342086</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.915764839556075</v>
+        <v>0.0710629180195522</v>
+      </c>
+      <c r="X15" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>30</v>
       </c>
       <c r="AA15" t="s">
         <v>30</v>
       </c>
-      <c r="AB15" t="s">
-        <v>30</v>
+      <c r="AB15" t="n">
+        <v>0.0201836141145918</v>
       </c>
       <c r="AC15" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.0201836141145918</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>3446</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="16">
@@ -19187,10 +18900,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>3447</v>
+        <v>3439</v>
       </c>
       <c r="C16" t="s">
-        <v>3425</v>
+        <v>3417</v>
       </c>
       <c r="D16" t="n">
         <v>860</v>
@@ -19247,37 +18960,28 @@
         <v>22234</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.36886011896274</v>
+        <v>-0.397594729526696</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.890769144630206</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.13391138189124</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-0.610302730428165</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-1.72921309908952</v>
+        <v>0.214710299142632</v>
+      </c>
+      <c r="X16" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>30</v>
       </c>
       <c r="AA16" t="s">
         <v>30</v>
       </c>
-      <c r="AB16" t="s">
-        <v>30</v>
+      <c r="AB16" t="n">
+        <v>0.0227575867456545</v>
       </c>
       <c r="AC16" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.0227575867456545</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>3448</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="17">
@@ -19285,10 +18989,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>3449</v>
+        <v>3441</v>
       </c>
       <c r="C17" t="s">
-        <v>3450</v>
+        <v>3442</v>
       </c>
       <c r="D17" t="n">
         <v>860</v>
@@ -19345,37 +19049,28 @@
         <v>17160</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.123938533208668</v>
+        <v>0.0729902790910264</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.13459086602202</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.68849524974874</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.902421102554467</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.30738313034747</v>
+        <v>0.119512474311302</v>
+      </c>
+      <c r="X17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>30</v>
       </c>
       <c r="AA17" t="s">
         <v>30</v>
       </c>
-      <c r="AB17" t="s">
-        <v>30</v>
+      <c r="AB17" t="n">
+        <v>0.0431005985483612</v>
       </c>
       <c r="AC17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.0431005985483612</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>3451</v>
+        <v>3443</v>
       </c>
     </row>
     <row r="18">
@@ -19383,7 +19078,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>3452</v>
+        <v>3444</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
@@ -19443,37 +19138,28 @@
         <v>68112</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.16823503275121</v>
+        <v>-0.0459376782675094</v>
       </c>
       <c r="W18" t="n">
-        <v>1.24028979182951</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.0405990124066677</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-0.127403648484491</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.66222379836146</v>
+        <v>0.0940294955711114</v>
+      </c>
+      <c r="X18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>30</v>
       </c>
       <c r="AA18" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" t="s">
-        <v>30</v>
+      <c r="AB18" t="n">
+        <v>0.0489111032794339</v>
       </c>
       <c r="AC18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.0489111032794339</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>3453</v>
+        <v>3445</v>
       </c>
     </row>
   </sheetData>
@@ -19504,34 +19190,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3454</v>
+        <v>3446</v>
       </c>
       <c r="G1" t="s">
         <v>1762</v>
       </c>
       <c r="H1" t="s">
-        <v>3455</v>
+        <v>3447</v>
       </c>
       <c r="I1" t="s">
-        <v>3456</v>
+        <v>3448</v>
       </c>
       <c r="J1" t="s">
         <v>1768</v>
       </c>
       <c r="K1" t="s">
-        <v>3457</v>
+        <v>3449</v>
       </c>
       <c r="L1" t="s">
-        <v>3458</v>
+        <v>3450</v>
       </c>
       <c r="M1" t="s">
-        <v>3459</v>
+        <v>3451</v>
       </c>
       <c r="N1" t="s">
-        <v>3460</v>
+        <v>3452</v>
       </c>
       <c r="O1" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="P1" t="s">
         <v>3244</v>
@@ -19551,33 +19237,33 @@
         <v>2136</v>
       </c>
       <c r="E2" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F2" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G2" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3464</v>
+        <v>3456</v>
       </c>
       <c r="K2" t="s">
-        <v>3465</v>
+        <v>3457</v>
       </c>
       <c r="L2" t="s">
-        <v>3464</v>
+        <v>3456</v>
       </c>
       <c r="M2" t="s">
-        <v>3466</v>
+        <v>3458</v>
       </c>
       <c r="N2" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O2" t="s">
-        <v>3468</v>
+        <v>3460</v>
       </c>
       <c r="P2" t="n">
         <v>10158</v>
@@ -19597,33 +19283,33 @@
         <v>1224</v>
       </c>
       <c r="E3" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F3" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G3" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3470</v>
+        <v>3462</v>
       </c>
       <c r="K3" t="s">
-        <v>3471</v>
+        <v>3463</v>
       </c>
       <c r="L3" t="s">
-        <v>3470</v>
+        <v>3462</v>
       </c>
       <c r="M3" t="s">
-        <v>3472</v>
+        <v>3464</v>
       </c>
       <c r="N3" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O3" t="s">
-        <v>3473</v>
+        <v>3465</v>
       </c>
       <c r="P3" t="n">
         <v>15096</v>
@@ -19643,33 +19329,33 @@
         <v>981</v>
       </c>
       <c r="E4" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F4" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G4" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3449</v>
+        <v>3441</v>
       </c>
       <c r="K4" t="s">
-        <v>3474</v>
+        <v>3466</v>
       </c>
       <c r="L4" t="s">
-        <v>3449</v>
+        <v>3441</v>
       </c>
       <c r="M4" t="s">
-        <v>3475</v>
+        <v>3467</v>
       </c>
       <c r="N4" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O4" t="s">
-        <v>3451</v>
+        <v>3443</v>
       </c>
       <c r="P4" t="n">
         <v>17849</v>
@@ -19689,33 +19375,33 @@
         <v>1851</v>
       </c>
       <c r="E5" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F5" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G5" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3447</v>
+        <v>3439</v>
       </c>
       <c r="K5" t="s">
-        <v>3476</v>
+        <v>3468</v>
       </c>
       <c r="L5" t="s">
-        <v>3447</v>
+        <v>3439</v>
       </c>
       <c r="M5" t="s">
-        <v>3477</v>
+        <v>3469</v>
       </c>
       <c r="N5" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O5" t="s">
-        <v>3448</v>
+        <v>3440</v>
       </c>
       <c r="P5" t="n">
         <v>23159</v>
@@ -19735,33 +19421,33 @@
         <v>945</v>
       </c>
       <c r="E6" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F6" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G6" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3427</v>
+        <v>3419</v>
       </c>
       <c r="K6" t="s">
-        <v>3478</v>
+        <v>3470</v>
       </c>
       <c r="L6" t="s">
-        <v>3427</v>
+        <v>3419</v>
       </c>
       <c r="M6" t="s">
-        <v>3479</v>
+        <v>3471</v>
       </c>
       <c r="N6" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O6" t="s">
-        <v>3428</v>
+        <v>3420</v>
       </c>
       <c r="P6" t="n">
         <v>25687</v>
@@ -19781,33 +19467,33 @@
         <v>3861</v>
       </c>
       <c r="E7" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F7" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G7" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3424</v>
+        <v>3416</v>
       </c>
       <c r="K7" t="s">
-        <v>3480</v>
+        <v>3472</v>
       </c>
       <c r="L7" t="s">
-        <v>3424</v>
+        <v>3416</v>
       </c>
       <c r="M7" t="s">
-        <v>3481</v>
+        <v>3473</v>
       </c>
       <c r="N7" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O7" t="s">
-        <v>3426</v>
+        <v>3418</v>
       </c>
       <c r="P7" t="n">
         <v>28757</v>
@@ -19827,33 +19513,33 @@
         <v>612</v>
       </c>
       <c r="E8" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F8" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G8" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3482</v>
+        <v>3474</v>
       </c>
       <c r="K8" t="s">
-        <v>3483</v>
+        <v>3475</v>
       </c>
       <c r="L8" t="s">
-        <v>3482</v>
+        <v>3474</v>
       </c>
       <c r="M8" t="s">
-        <v>3484</v>
+        <v>3476</v>
       </c>
       <c r="N8" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O8" t="s">
-        <v>3485</v>
+        <v>3477</v>
       </c>
       <c r="P8" t="n">
         <v>31388</v>
@@ -19873,33 +19559,33 @@
         <v>2148</v>
       </c>
       <c r="E9" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F9" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G9" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3431</v>
+        <v>3423</v>
       </c>
       <c r="K9" t="s">
-        <v>3486</v>
+        <v>3478</v>
       </c>
       <c r="L9" t="s">
-        <v>3431</v>
+        <v>3423</v>
       </c>
       <c r="M9" t="s">
-        <v>3487</v>
+        <v>3479</v>
       </c>
       <c r="N9" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O9" t="s">
-        <v>3432</v>
+        <v>3424</v>
       </c>
       <c r="P9" t="n">
         <v>33034</v>
@@ -19919,33 +19605,33 @@
         <v>1872</v>
       </c>
       <c r="E10" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F10" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G10" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3488</v>
+        <v>3480</v>
       </c>
       <c r="K10" t="s">
-        <v>3489</v>
+        <v>3481</v>
       </c>
       <c r="L10" t="s">
-        <v>3488</v>
+        <v>3480</v>
       </c>
       <c r="M10" t="s">
-        <v>3490</v>
+        <v>3482</v>
       </c>
       <c r="N10" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O10" t="s">
-        <v>3491</v>
+        <v>3483</v>
       </c>
       <c r="P10" t="n">
         <v>35478</v>
@@ -19965,33 +19651,33 @@
         <v>1455</v>
       </c>
       <c r="E11" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F11" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G11" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3420</v>
+        <v>3412</v>
       </c>
       <c r="K11" t="s">
-        <v>3492</v>
+        <v>3484</v>
       </c>
       <c r="L11" t="s">
-        <v>3420</v>
+        <v>3412</v>
       </c>
       <c r="M11" t="s">
-        <v>3493</v>
+        <v>3485</v>
       </c>
       <c r="N11" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O11" t="s">
-        <v>3421</v>
+        <v>3413</v>
       </c>
       <c r="P11" t="n">
         <v>37426</v>
@@ -20011,13 +19697,13 @@
         <v>3075</v>
       </c>
       <c r="E12" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F12" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G12" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
@@ -20025,16 +19711,16 @@
         <v>98</v>
       </c>
       <c r="K12" t="s">
-        <v>3494</v>
+        <v>3486</v>
       </c>
       <c r="L12" t="s">
         <v>98</v>
       </c>
       <c r="M12" t="s">
-        <v>3495</v>
+        <v>3487</v>
       </c>
       <c r="N12" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O12" t="s">
         <v>99</v>
@@ -20057,33 +19743,33 @@
         <v>3873</v>
       </c>
       <c r="E13" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F13" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G13" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3429</v>
+        <v>3421</v>
       </c>
       <c r="K13" t="s">
-        <v>3496</v>
+        <v>3488</v>
       </c>
       <c r="L13" t="s">
-        <v>3429</v>
+        <v>3421</v>
       </c>
       <c r="M13" t="s">
-        <v>3497</v>
+        <v>3489</v>
       </c>
       <c r="N13" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O13" t="s">
-        <v>3430</v>
+        <v>3422</v>
       </c>
       <c r="P13" t="n">
         <v>44359</v>
@@ -20103,33 +19789,33 @@
         <v>816</v>
       </c>
       <c r="E14" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F14" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G14" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3498</v>
+        <v>3490</v>
       </c>
       <c r="K14" t="s">
-        <v>3499</v>
+        <v>3491</v>
       </c>
       <c r="L14" t="s">
-        <v>3498</v>
+        <v>3490</v>
       </c>
       <c r="M14" t="s">
-        <v>3500</v>
+        <v>3492</v>
       </c>
       <c r="N14" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O14" t="s">
-        <v>3501</v>
+        <v>3493</v>
       </c>
       <c r="P14" t="n">
         <v>47564</v>
@@ -20149,33 +19835,33 @@
         <v>762</v>
       </c>
       <c r="E15" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F15" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G15" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3502</v>
+        <v>3494</v>
       </c>
       <c r="K15" t="s">
-        <v>3503</v>
+        <v>3495</v>
       </c>
       <c r="L15" t="s">
-        <v>3502</v>
+        <v>3494</v>
       </c>
       <c r="M15" t="s">
-        <v>3504</v>
+        <v>3496</v>
       </c>
       <c r="N15" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O15" t="s">
-        <v>3505</v>
+        <v>3497</v>
       </c>
       <c r="P15" t="n">
         <v>48574</v>
@@ -20195,33 +19881,33 @@
         <v>804</v>
       </c>
       <c r="E16" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F16" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G16" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3445</v>
+        <v>3437</v>
       </c>
       <c r="K16" t="s">
-        <v>3506</v>
+        <v>3498</v>
       </c>
       <c r="L16" t="s">
-        <v>3445</v>
+        <v>3437</v>
       </c>
       <c r="M16" t="s">
-        <v>3507</v>
+        <v>3499</v>
       </c>
       <c r="N16" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O16" t="s">
-        <v>3446</v>
+        <v>3438</v>
       </c>
       <c r="P16" t="n">
         <v>49408</v>
@@ -20241,33 +19927,33 @@
         <v>3303</v>
       </c>
       <c r="E17" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F17" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G17" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3508</v>
+        <v>3500</v>
       </c>
       <c r="K17" t="s">
-        <v>3509</v>
+        <v>3501</v>
       </c>
       <c r="L17" t="s">
-        <v>3508</v>
+        <v>3500</v>
       </c>
       <c r="M17" t="s">
-        <v>3510</v>
+        <v>3502</v>
       </c>
       <c r="N17" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O17" t="s">
-        <v>3511</v>
+        <v>3503</v>
       </c>
       <c r="P17" t="n">
         <v>51702</v>
@@ -20287,33 +19973,33 @@
         <v>1899</v>
       </c>
       <c r="E18" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F18" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G18" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3512</v>
+        <v>3504</v>
       </c>
       <c r="K18" t="s">
-        <v>3513</v>
+        <v>3505</v>
       </c>
       <c r="L18" t="s">
-        <v>3512</v>
+        <v>3504</v>
       </c>
       <c r="M18" t="s">
-        <v>3514</v>
+        <v>3506</v>
       </c>
       <c r="N18" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O18" t="s">
-        <v>3515</v>
+        <v>3507</v>
       </c>
       <c r="P18" t="n">
         <v>54653</v>
@@ -20333,33 +20019,33 @@
         <v>7425</v>
       </c>
       <c r="E19" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F19" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G19" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3443</v>
+        <v>3435</v>
       </c>
       <c r="K19" t="s">
-        <v>3516</v>
+        <v>3508</v>
       </c>
       <c r="L19" t="s">
-        <v>3443</v>
+        <v>3435</v>
       </c>
       <c r="M19" t="s">
-        <v>3517</v>
+        <v>3509</v>
       </c>
       <c r="N19" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O19" t="s">
-        <v>3444</v>
+        <v>3436</v>
       </c>
       <c r="P19" t="n">
         <v>59647</v>
@@ -20379,33 +20065,33 @@
         <v>3537</v>
       </c>
       <c r="E20" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F20" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G20" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3422</v>
+        <v>3414</v>
       </c>
       <c r="K20" t="s">
-        <v>3518</v>
+        <v>3510</v>
       </c>
       <c r="L20" t="s">
-        <v>3422</v>
+        <v>3414</v>
       </c>
       <c r="M20" t="s">
-        <v>3519</v>
+        <v>3511</v>
       </c>
       <c r="N20" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O20" t="s">
-        <v>3423</v>
+        <v>3415</v>
       </c>
       <c r="P20" t="n">
         <v>65698</v>
@@ -20425,33 +20111,33 @@
         <v>1989</v>
       </c>
       <c r="E21" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F21" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G21" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3452</v>
+        <v>3444</v>
       </c>
       <c r="K21" t="s">
-        <v>3520</v>
+        <v>3512</v>
       </c>
       <c r="L21" t="s">
-        <v>3452</v>
+        <v>3444</v>
       </c>
       <c r="M21" t="s">
-        <v>3521</v>
+        <v>3513</v>
       </c>
       <c r="N21" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O21" t="s">
-        <v>3453</v>
+        <v>3445</v>
       </c>
       <c r="P21" t="n">
         <v>69226</v>
@@ -20471,13 +20157,13 @@
         <v>3132</v>
       </c>
       <c r="E22" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F22" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G22" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
@@ -20485,16 +20171,16 @@
         <v>118</v>
       </c>
       <c r="K22" t="s">
-        <v>3522</v>
+        <v>3514</v>
       </c>
       <c r="L22" t="s">
         <v>118</v>
       </c>
       <c r="M22" t="s">
-        <v>3523</v>
+        <v>3515</v>
       </c>
       <c r="N22" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O22" t="s">
         <v>119</v>
@@ -20517,33 +20203,33 @@
         <v>603</v>
       </c>
       <c r="E23" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F23" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G23" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3524</v>
+        <v>3516</v>
       </c>
       <c r="K23" t="s">
-        <v>3525</v>
+        <v>3517</v>
       </c>
       <c r="L23" t="s">
-        <v>3524</v>
+        <v>3516</v>
       </c>
       <c r="M23" t="s">
-        <v>3526</v>
+        <v>3518</v>
       </c>
       <c r="N23" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O23" t="s">
-        <v>3527</v>
+        <v>3519</v>
       </c>
       <c r="P23" t="n">
         <v>75233</v>
@@ -20563,33 +20249,33 @@
         <v>1212</v>
       </c>
       <c r="E24" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F24" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G24" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3436</v>
+        <v>3428</v>
       </c>
       <c r="K24" t="s">
-        <v>3528</v>
+        <v>3520</v>
       </c>
       <c r="L24" t="s">
-        <v>3436</v>
+        <v>3428</v>
       </c>
       <c r="M24" t="s">
-        <v>3529</v>
+        <v>3521</v>
       </c>
       <c r="N24" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O24" t="s">
-        <v>3437</v>
+        <v>3429</v>
       </c>
       <c r="P24" t="n">
         <v>76426</v>
@@ -20609,33 +20295,33 @@
         <v>1389</v>
       </c>
       <c r="E25" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F25" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G25" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3440</v>
+        <v>3432</v>
       </c>
       <c r="K25" t="s">
-        <v>3530</v>
+        <v>3522</v>
       </c>
       <c r="L25" t="s">
-        <v>3440</v>
+        <v>3432</v>
       </c>
       <c r="M25" t="s">
-        <v>3531</v>
+        <v>3523</v>
       </c>
       <c r="N25" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O25" t="s">
-        <v>3442</v>
+        <v>3434</v>
       </c>
       <c r="P25" t="n">
         <v>77952</v>
@@ -20655,33 +20341,33 @@
         <v>1017</v>
       </c>
       <c r="E26" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F26" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G26" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3438</v>
+        <v>3430</v>
       </c>
       <c r="K26" t="s">
-        <v>3532</v>
+        <v>3524</v>
       </c>
       <c r="L26" t="s">
-        <v>3438</v>
+        <v>3430</v>
       </c>
       <c r="M26" t="s">
-        <v>3533</v>
+        <v>3525</v>
       </c>
       <c r="N26" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O26" t="s">
-        <v>3439</v>
+        <v>3431</v>
       </c>
       <c r="P26" t="n">
         <v>79374</v>
@@ -20701,33 +20387,33 @@
         <v>378</v>
       </c>
       <c r="E27" t="s">
-        <v>3462</v>
+        <v>3454</v>
       </c>
       <c r="F27" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G27" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3433</v>
+        <v>3425</v>
       </c>
       <c r="K27" t="s">
-        <v>3534</v>
+        <v>3526</v>
       </c>
       <c r="L27" t="s">
-        <v>3433</v>
+        <v>3425</v>
       </c>
       <c r="M27" t="s">
-        <v>3535</v>
+        <v>3527</v>
       </c>
       <c r="N27" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O27" t="s">
-        <v>3435</v>
+        <v>3427</v>
       </c>
       <c r="P27" t="n">
         <v>80348</v>
@@ -20747,33 +20433,33 @@
         <v>1605</v>
       </c>
       <c r="E28" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F28" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G28" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3536</v>
+        <v>3528</v>
       </c>
       <c r="K28" t="s">
-        <v>3537</v>
+        <v>3529</v>
       </c>
       <c r="L28" t="s">
-        <v>3536</v>
+        <v>3528</v>
       </c>
       <c r="M28" t="s">
-        <v>3538</v>
+        <v>3530</v>
       </c>
       <c r="N28" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O28" t="s">
-        <v>3539</v>
+        <v>3531</v>
       </c>
       <c r="P28" t="n">
         <v>81837</v>
@@ -20793,33 +20479,33 @@
         <v>604</v>
       </c>
       <c r="E29" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F29" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G29" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>3540</v>
+        <v>3532</v>
       </c>
       <c r="K29" t="s">
-        <v>3541</v>
+        <v>3533</v>
       </c>
       <c r="L29" t="s">
-        <v>3540</v>
+        <v>3532</v>
       </c>
       <c r="M29" t="s">
-        <v>3542</v>
+        <v>3534</v>
       </c>
       <c r="N29" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O29" t="s">
-        <v>3543</v>
+        <v>3535</v>
       </c>
       <c r="P29" t="n">
         <v>83248</v>
@@ -20839,33 +20525,33 @@
         <v>1200</v>
       </c>
       <c r="E30" t="s">
-        <v>3469</v>
+        <v>3461</v>
       </c>
       <c r="F30" t="s">
-        <v>3463</v>
+        <v>3455</v>
       </c>
       <c r="G30" t="s">
-        <v>3461</v>
+        <v>3453</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3544</v>
+        <v>3536</v>
       </c>
       <c r="K30" t="s">
-        <v>3545</v>
+        <v>3537</v>
       </c>
       <c r="L30" t="s">
-        <v>3544</v>
+        <v>3536</v>
       </c>
       <c r="M30" t="s">
-        <v>3546</v>
+        <v>3538</v>
       </c>
       <c r="N30" t="s">
-        <v>3467</v>
+        <v>3459</v>
       </c>
       <c r="O30" t="s">
-        <v>3547</v>
+        <v>3539</v>
       </c>
       <c r="P30" t="n">
         <v>85304</v>
